--- a/backend/data/financials_by_company/1IK.F.xlsx
+++ b/backend/data/financials_by_company/1IK.F.xlsx
@@ -4148,10 +4148,8 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>92127</t>
-        </is>
+      <c r="E2" t="n">
+        <v>92127</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4481,7 +4479,7 @@
         <v>199978000</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0.038</v>
